--- a/Personal_Logs/Anime_Watch_List.xlsx
+++ b/Personal_Logs/Anime_Watch_List.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="30">
   <si>
     <t>片名</t>
   </si>
@@ -42,27 +42,18 @@
     <t>完结观影日期</t>
   </si>
   <si>
-    <t>Serial Experiments Lain</t>
-  </si>
-  <si>
     <t>日本</t>
   </si>
   <si>
     <t>在看</t>
   </si>
   <si>
-    <t xml:space="preserve">末日后酒店 </t>
-  </si>
-  <si>
     <t>小林家的龙女仆</t>
   </si>
   <si>
     <t>13+1</t>
   </si>
   <si>
-    <t>完结</t>
-  </si>
-  <si>
     <t>小林家的龙女仆S</t>
   </si>
   <si>
@@ -75,13 +66,63 @@
     <t>神奇数字马戏团</t>
   </si>
   <si>
-    <t>澳大利亚</t>
-  </si>
-  <si>
-    <t>百变小樱第一季</t>
-  </si>
-  <si>
-    <t>完结</t>
+    <t>百变小樱</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>百变小樱：库洛牌篇</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>百变小樱：小樱牌篇</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>已看</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>链接</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>玲音</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://movie.douban.com/subject/1417233/</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>末日后酒店</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://movie.douban.com/subject/37028590/</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://movie.douban.com/subject/26899726/</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://movie.douban.com/subject/30459061/</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://movie.douban.com/subject/35880801/</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://movie.douban.com/subject/36621210/</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>美国/澳大利亚</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://movie.douban.com/subject/1465035/</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -89,7 +130,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -244,6 +285,15 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="等线"/>
       <family val="2"/>
       <charset val="134"/>
@@ -547,7 +597,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -674,8 +724,11 @@
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -685,8 +738,11 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="42" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="43">
     <cellStyle name="20% - 着色 1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - 着色 2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - 着色 3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -712,6 +768,7 @@
     <cellStyle name="标题 4" xfId="5" builtinId="19" customBuiltin="1"/>
     <cellStyle name="差" xfId="7" builtinId="27" customBuiltin="1"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="超链接" xfId="42" builtinId="8"/>
     <cellStyle name="好" xfId="6" builtinId="26" customBuiltin="1"/>
     <cellStyle name="汇总" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="计算" xfId="11" builtinId="22" customBuiltin="1"/>
@@ -1006,19 +1063,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.21875" style="1" customWidth="1"/>
     <col min="4" max="4" width="7.5546875" style="1" customWidth="1"/>
     <col min="5" max="5" width="8.88671875" style="1"/>
     <col min="6" max="7" width="13.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.88671875" style="1"/>
+    <col min="8" max="8" width="46.77734375" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1040,42 +1098,48 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="1" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="B2" s="2">
         <v>35982</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D2" s="1">
         <v>13</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" s="2">
         <v>45947</v>
       </c>
+      <c r="H2" s="3" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B3" s="2">
         <v>45755</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D3" s="1">
         <v>12</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F3" s="2">
         <v>45959</v>
@@ -1083,22 +1147,25 @@
       <c r="G3" s="2">
         <v>46103</v>
       </c>
+      <c r="H3" s="3" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B4" s="2">
         <v>42746</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F4" s="2">
         <v>46092</v>
@@ -1106,22 +1173,25 @@
       <c r="G4" s="2">
         <v>46096</v>
       </c>
+      <c r="H4" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B5" s="2">
         <v>44384</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F5" s="2">
         <v>46096</v>
@@ -1129,42 +1199,48 @@
       <c r="G5" s="2">
         <v>46099</v>
       </c>
+      <c r="H5" s="3" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B6" s="2">
         <v>44931</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D6" s="1">
         <v>12</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F6" s="2">
         <v>46145</v>
       </c>
+      <c r="H6" s="3" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B7" s="2">
         <v>45212</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="D7" s="1">
         <v>9</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F7" s="2">
         <v>45214</v>
@@ -1172,32 +1248,102 @@
       <c r="G7" s="2">
         <v>46195</v>
       </c>
+      <c r="H7" s="3" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B8" s="2">
         <v>35892</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D8" s="1">
         <v>35</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F8" s="2">
         <v>46228</v>
       </c>
       <c r="G8" s="2">
         <v>46237</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="2">
+        <v>36263</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="1">
+        <v>11</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" s="2">
+        <v>46237</v>
+      </c>
+      <c r="G9" s="2">
+        <v>46240</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="2">
+        <v>36410</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="1">
+        <v>24</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="2">
+        <v>46240</v>
+      </c>
+      <c r="G10" s="2">
+        <v>46244</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9:H10" r:id="rId8" display="https://movie.douban.com/subject/1465035/"/>
+    <hyperlink ref="H9" r:id="rId9"/>
+    <hyperlink ref="H10" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>